--- a/research/traditional_assets/database/data/norway/norway_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08690000000000001</v>
+        <v>0.07615</v>
       </c>
       <c r="E2">
-        <v>0.1395</v>
+        <v>0.03545</v>
       </c>
       <c r="F2">
-        <v>0.0192</v>
+        <v>-0.0429</v>
       </c>
       <c r="G2">
-        <v>0.208226454497991</v>
+        <v>0.3388048432650093</v>
       </c>
       <c r="H2">
-        <v>0.208226454497991</v>
+        <v>0.3388048432650093</v>
       </c>
       <c r="I2">
-        <v>0.2619571879327174</v>
+        <v>0.2035457621431168</v>
       </c>
       <c r="J2">
-        <v>0.2146823507393182</v>
+        <v>0.1661652055041372</v>
       </c>
       <c r="K2">
-        <v>916.5</v>
+        <v>569.9000000000001</v>
       </c>
       <c r="L2">
-        <v>0.2080448550609493</v>
+        <v>0.1593635524733648</v>
       </c>
       <c r="M2">
-        <v>641.35</v>
+        <v>349.38</v>
       </c>
       <c r="N2">
-        <v>0.04874183962730182</v>
+        <v>0.03233413232395214</v>
       </c>
       <c r="O2">
-        <v>0.6997817785051827</v>
+        <v>0.6130549219161255</v>
       </c>
       <c r="P2">
-        <v>638.9</v>
+        <v>347.3</v>
       </c>
       <c r="Q2">
-        <v>0.0485556425319765</v>
+        <v>0.03214163419803245</v>
       </c>
       <c r="R2">
-        <v>0.6971085651936716</v>
+        <v>0.6094051587997894</v>
       </c>
       <c r="S2">
-        <v>2.450000000000045</v>
+        <v>2.080000000000013</v>
       </c>
       <c r="T2">
-        <v>0.003820067046074757</v>
+        <v>0.005953403171332109</v>
       </c>
       <c r="U2">
-        <v>361.9</v>
+        <v>228.45</v>
       </c>
       <c r="V2">
-        <v>0.02750397093805337</v>
+        <v>0.02114240233959261</v>
       </c>
       <c r="W2">
-        <v>0.4435190387210183</v>
+        <v>0.1462056908322709</v>
       </c>
       <c r="X2">
-        <v>0.04578306778301765</v>
+        <v>0.07701262529387273</v>
       </c>
       <c r="Y2">
-        <v>0.3977359709380007</v>
+        <v>0.06919306553839816</v>
       </c>
       <c r="Z2">
-        <v>1.773177535108939</v>
+        <v>1.173992974623289</v>
       </c>
       <c r="AA2">
-        <v>0.3741990080836057</v>
+        <v>0.1519073785554722</v>
       </c>
       <c r="AB2">
-        <v>0.04378769018535186</v>
+        <v>0.07434653357629793</v>
       </c>
       <c r="AC2">
-        <v>0.3304113178982538</v>
+        <v>0.07756084497917431</v>
       </c>
       <c r="AD2">
-        <v>565.4</v>
+        <v>446.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>565.4</v>
+        <v>446.9</v>
       </c>
       <c r="AG2">
-        <v>203.4999999999999</v>
+        <v>218.45</v>
       </c>
       <c r="AH2">
-        <v>0.04119940248478886</v>
+        <v>0.03971667762748618</v>
       </c>
       <c r="AI2">
-        <v>0.1476240208877284</v>
+        <v>0.1484816266861585</v>
       </c>
       <c r="AJ2">
-        <v>0.01523021195066459</v>
+        <v>0.01981630570359451</v>
       </c>
       <c r="AK2">
-        <v>0.0586776621204694</v>
+        <v>0.07854099627878547</v>
       </c>
       <c r="AL2">
-        <v>28.3</v>
+        <v>30.2</v>
       </c>
       <c r="AM2">
-        <v>28.3</v>
+        <v>30.2</v>
       </c>
       <c r="AN2">
-        <v>0.4796810044964792</v>
+        <v>0.6001880204136448</v>
       </c>
       <c r="AO2">
-        <v>40.7773851590106</v>
+        <v>24.10264900662252</v>
       </c>
       <c r="AP2">
-        <v>0.1726478323576821</v>
+        <v>0.2933789954337899</v>
       </c>
       <c r="AQ2">
-        <v>40.7773851590106</v>
+        <v>24.10264900662252</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Protector Forsikring ASA (OB:PROT)</t>
+          <t>Gjensidige Forsikring ASA (OB:GJF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,115 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.139</v>
+        <v>0.0403</v>
       </c>
       <c r="E3">
-        <v>0.215</v>
+        <v>0.0441</v>
+      </c>
+      <c r="F3">
+        <v>-0.0429</v>
       </c>
       <c r="G3">
-        <v>0.1815909425084546</v>
+        <v>0.3421387339790626</v>
       </c>
       <c r="H3">
-        <v>0.1815909425084546</v>
+        <v>0.3421387339790626</v>
       </c>
       <c r="I3">
-        <v>0.2626084399353036</v>
+        <v>0.2194175390535825</v>
       </c>
       <c r="J3">
-        <v>0.221143949419203</v>
+        <v>0.1798431649852504</v>
       </c>
       <c r="K3">
-        <v>161.7</v>
+        <v>526.7</v>
       </c>
       <c r="L3">
-        <v>0.2377591530657256</v>
+        <v>0.1717705377816913</v>
       </c>
       <c r="M3">
-        <v>59.8</v>
+        <v>249.48</v>
       </c>
       <c r="N3">
-        <v>0.05900345337937839</v>
+        <v>0.02557877253060472</v>
       </c>
       <c r="O3">
-        <v>0.3698206555349413</v>
+        <v>0.4736662236567306</v>
       </c>
       <c r="P3">
-        <v>59.8</v>
+        <v>247.4</v>
       </c>
       <c r="Q3">
-        <v>0.05900345337937839</v>
+        <v>0.02536551356450058</v>
       </c>
       <c r="R3">
-        <v>0.3698206555349413</v>
+        <v>0.469717106512246</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.080000000000013</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.008337341670675054</v>
       </c>
       <c r="U3">
-        <v>11.6</v>
+        <v>218.9</v>
       </c>
       <c r="V3">
-        <v>0.01144548593981253</v>
+        <v>0.02244345561547768</v>
       </c>
       <c r="W3">
-        <v>0.5882138959621681</v>
+        <v>0.1837047888109937</v>
       </c>
       <c r="X3">
-        <v>0.04696897419320526</v>
+        <v>0.07595571135854388</v>
       </c>
       <c r="Y3">
-        <v>0.5412449217689629</v>
+        <v>0.1077490774524498</v>
       </c>
       <c r="Z3">
-        <v>1.697237403608595</v>
+        <v>1.217897287206578</v>
       </c>
       <c r="AA3">
-        <v>0.3753337825359986</v>
+        <v>0.2190305027581814</v>
       </c>
       <c r="AB3">
-        <v>0.04386595276930857</v>
+        <v>0.07466872020429142</v>
       </c>
       <c r="AC3">
-        <v>0.33146782976669</v>
+        <v>0.14436178255389</v>
       </c>
       <c r="AD3">
-        <v>142.6</v>
+        <v>332.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>142.6</v>
+        <v>332.3</v>
       </c>
       <c r="AG3">
-        <v>131</v>
+        <v>113.4</v>
       </c>
       <c r="AH3">
-        <v>0.1233457313381195</v>
+        <v>0.03294763873603221</v>
       </c>
       <c r="AI3">
-        <v>0.2640740740740741</v>
+        <v>0.1261435675511521</v>
       </c>
       <c r="AJ3">
-        <v>0.1144604630843163</v>
+        <v>0.01149308793124417</v>
       </c>
       <c r="AK3">
-        <v>0.2479182437547313</v>
+        <v>0.04694874554939141</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="AN3">
-        <v>0.7913429522752498</v>
+        <v>0.4829941860465116</v>
+      </c>
+      <c r="AO3">
+        <v>22.27814569536424</v>
       </c>
       <c r="AP3">
-        <v>0.7269700332963375</v>
+        <v>0.1648255813953488</v>
+      </c>
+      <c r="AQ3">
+        <v>22.27814569536424</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gjensidige Forsikring ASA (OB:GJF)</t>
+          <t>Protector Forsikring ASA (OB:PROT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,124 +862,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0348</v>
+        <v>0.112</v>
       </c>
       <c r="E4">
-        <v>0.064</v>
-      </c>
-      <c r="F4">
-        <v>0.0192</v>
+        <v>0.0268</v>
       </c>
       <c r="G4">
-        <v>0.2130892301084505</v>
+        <v>0.318752451941938</v>
       </c>
       <c r="H4">
-        <v>0.2130892301084505</v>
+        <v>0.318752451941938</v>
       </c>
       <c r="I4">
-        <v>0.2618382905615806</v>
+        <v>0.1080816006276971</v>
       </c>
       <c r="J4">
-        <v>0.2086744184519914</v>
+        <v>0.0878775990584543</v>
       </c>
       <c r="K4">
-        <v>754.8</v>
+        <v>43.2</v>
       </c>
       <c r="L4">
-        <v>0.2026199935573929</v>
+        <v>0.08473911337779522</v>
       </c>
       <c r="M4">
-        <v>581.5500000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="N4">
-        <v>0.04788547996640483</v>
+        <v>0.09497100484836961</v>
       </c>
       <c r="O4">
-        <v>0.770468998410175</v>
+        <v>2.3125</v>
       </c>
       <c r="P4">
-        <v>579.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.04768374421553612</v>
+        <v>0.09497100484836961</v>
       </c>
       <c r="R4">
-        <v>0.7672231054583997</v>
+        <v>2.3125</v>
       </c>
       <c r="S4">
-        <v>2.450000000000045</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.004212879374086571</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>350.3</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="V4">
-        <v>0.02884409531808376</v>
+        <v>0.009078809772792091</v>
       </c>
       <c r="W4">
-        <v>0.2988241814798686</v>
+        <v>0.1087065928535481</v>
       </c>
       <c r="X4">
-        <v>0.04459716137283005</v>
+        <v>0.07806953922920157</v>
       </c>
       <c r="Y4">
-        <v>0.2542270201070385</v>
+        <v>0.0306370536243465</v>
       </c>
       <c r="Z4">
-        <v>1.787781350482315</v>
+        <v>0.9647993943981833</v>
       </c>
       <c r="AA4">
-        <v>0.3730642336312128</v>
+        <v>0.08478425435276307</v>
       </c>
       <c r="AB4">
-        <v>0.04370942760139515</v>
+        <v>0.07402434694830444</v>
       </c>
       <c r="AC4">
-        <v>0.3293548060298177</v>
+        <v>0.01075990740445863</v>
       </c>
       <c r="AD4">
-        <v>422.8</v>
+        <v>114.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>422.8</v>
+        <v>114.6</v>
       </c>
       <c r="AG4">
-        <v>72.5</v>
+        <v>105.05</v>
       </c>
       <c r="AH4">
-        <v>0.03364259910562249</v>
+        <v>0.09824260608658379</v>
       </c>
       <c r="AI4">
-        <v>0.1285106382978723</v>
+        <v>0.3051930758988016</v>
       </c>
       <c r="AJ4">
-        <v>0.005934305195177251</v>
+        <v>0.09079908379791693</v>
       </c>
       <c r="AK4">
-        <v>0.02466238051501854</v>
+        <v>0.2870610739172018</v>
       </c>
       <c r="AL4">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.4234351527290937</v>
-      </c>
-      <c r="AO4">
-        <v>34.46643109540636</v>
+        <v>2.024734982332155</v>
       </c>
       <c r="AP4">
-        <v>0.07260891337005508</v>
-      </c>
-      <c r="AQ4">
-        <v>34.46643109540636</v>
+        <v>1.856007067137809</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07615</v>
+        <v>0.1692</v>
       </c>
       <c r="E2">
-        <v>0.03545</v>
+        <v>0.27625</v>
       </c>
       <c r="F2">
-        <v>-0.0429</v>
+        <v>0.115</v>
       </c>
       <c r="G2">
-        <v>0.3388048432650093</v>
+        <v>0.1732696125963892</v>
       </c>
       <c r="H2">
-        <v>0.3388048432650093</v>
+        <v>0.1732696125963892</v>
       </c>
       <c r="I2">
-        <v>0.2035457621431168</v>
+        <v>0.1773791383848178</v>
       </c>
       <c r="J2">
-        <v>0.1661652055041372</v>
+        <v>0.1425825858772812</v>
       </c>
       <c r="K2">
-        <v>569.9000000000001</v>
+        <v>597.9</v>
       </c>
       <c r="L2">
-        <v>0.1593635524733648</v>
+        <v>0.1380385094888489</v>
       </c>
       <c r="M2">
-        <v>349.38</v>
+        <v>471.9</v>
       </c>
       <c r="N2">
-        <v>0.03233413232395214</v>
+        <v>0.04407438194061773</v>
       </c>
       <c r="O2">
-        <v>0.6130549219161255</v>
+        <v>0.7892624184646262</v>
       </c>
       <c r="P2">
-        <v>347.3</v>
+        <v>470</v>
       </c>
       <c r="Q2">
-        <v>0.03214163419803245</v>
+        <v>0.04389692628118316</v>
       </c>
       <c r="R2">
-        <v>0.6094051587997894</v>
+        <v>0.7860846295367119</v>
       </c>
       <c r="S2">
-        <v>2.080000000000013</v>
+        <v>1.899999999999977</v>
       </c>
       <c r="T2">
-        <v>0.005953403171332109</v>
+        <v>0.004026276753549433</v>
       </c>
       <c r="U2">
-        <v>228.45</v>
+        <v>420.1</v>
       </c>
       <c r="V2">
-        <v>0.02114240233959261</v>
+        <v>0.0392363802781384</v>
       </c>
       <c r="W2">
-        <v>0.1462056908322709</v>
+        <v>0.274985321756049</v>
       </c>
       <c r="X2">
-        <v>0.07701262529387273</v>
+        <v>0.06881269328995346</v>
       </c>
       <c r="Y2">
-        <v>0.06919306553839816</v>
+        <v>0.2061726284660955</v>
       </c>
       <c r="Z2">
-        <v>1.173992974623289</v>
+        <v>1.884241435562806</v>
       </c>
       <c r="AA2">
-        <v>0.1519073785554722</v>
+        <v>0.2520212482063691</v>
       </c>
       <c r="AB2">
-        <v>0.07434653357629793</v>
+        <v>0.06685704118264152</v>
       </c>
       <c r="AC2">
-        <v>0.07756084497917431</v>
+        <v>0.1851642070237276</v>
       </c>
       <c r="AD2">
-        <v>446.9</v>
+        <v>520.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>446.9</v>
+        <v>520.5</v>
       </c>
       <c r="AG2">
-        <v>218.45</v>
+        <v>100.4</v>
       </c>
       <c r="AH2">
-        <v>0.03971667762748618</v>
+        <v>0.04635979835046405</v>
       </c>
       <c r="AI2">
-        <v>0.1484816266861585</v>
+        <v>0.1702872472682065</v>
       </c>
       <c r="AJ2">
-        <v>0.01981630570359451</v>
+        <v>0.009290016932998996</v>
       </c>
       <c r="AK2">
-        <v>0.07854099627878547</v>
+        <v>0.03808078892471081</v>
       </c>
       <c r="AL2">
-        <v>30.2</v>
+        <v>38.55</v>
       </c>
       <c r="AM2">
-        <v>30.2</v>
+        <v>38.55</v>
       </c>
       <c r="AN2">
-        <v>0.6001880204136448</v>
+        <v>0.655293969532922</v>
       </c>
       <c r="AO2">
-        <v>24.10264900662252</v>
+        <v>19.92996108949416</v>
       </c>
       <c r="AP2">
-        <v>0.2933789954337899</v>
+        <v>0.126400604305678</v>
       </c>
       <c r="AQ2">
-        <v>24.10264900662252</v>
+        <v>19.92996108949416</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0403</v>
+        <v>0.0664</v>
       </c>
       <c r="E3">
-        <v>0.0441</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="F3">
-        <v>-0.0429</v>
+        <v>0.115</v>
       </c>
       <c r="G3">
-        <v>0.3421387339790626</v>
+        <v>0.1810424677912819</v>
       </c>
       <c r="H3">
-        <v>0.3421387339790626</v>
+        <v>0.1810424677912819</v>
       </c>
       <c r="I3">
-        <v>0.2194175390535825</v>
+        <v>0.1862351587279311</v>
       </c>
       <c r="J3">
-        <v>0.1798431649852504</v>
+        <v>0.1428332515075466</v>
       </c>
       <c r="K3">
-        <v>526.7</v>
+        <v>512.5</v>
       </c>
       <c r="L3">
-        <v>0.1717705377816913</v>
+        <v>0.1438515732450108</v>
       </c>
       <c r="M3">
-        <v>249.48</v>
+        <v>394.6</v>
       </c>
       <c r="N3">
-        <v>0.02557877253060472</v>
+        <v>0.04268530137164121</v>
       </c>
       <c r="O3">
-        <v>0.4736662236567306</v>
+        <v>0.769951219512195</v>
       </c>
       <c r="P3">
-        <v>247.4</v>
+        <v>392.7</v>
       </c>
       <c r="Q3">
-        <v>0.02536551356450058</v>
+        <v>0.04247977153736316</v>
       </c>
       <c r="R3">
-        <v>0.469717106512246</v>
+        <v>0.7662439024390244</v>
       </c>
       <c r="S3">
-        <v>2.080000000000013</v>
+        <v>1.899999999999977</v>
       </c>
       <c r="T3">
-        <v>0.008337341670675054</v>
+        <v>0.004815002534211803</v>
       </c>
       <c r="U3">
-        <v>218.9</v>
+        <v>409.7</v>
       </c>
       <c r="V3">
-        <v>0.02244345561547768</v>
+        <v>0.04431872268616676</v>
       </c>
       <c r="W3">
-        <v>0.1837047888109937</v>
+        <v>0.2226421651679048</v>
       </c>
       <c r="X3">
-        <v>0.07595571135854388</v>
+        <v>0.06840939722315574</v>
       </c>
       <c r="Y3">
-        <v>0.1077490774524498</v>
+        <v>0.154232767944749</v>
       </c>
       <c r="Z3">
-        <v>1.217897287206578</v>
+        <v>1.843284354304636</v>
       </c>
       <c r="AA3">
-        <v>0.2190305027581814</v>
+        <v>0.2632822977783196</v>
       </c>
       <c r="AB3">
-        <v>0.07466872020429142</v>
+        <v>0.06701672385955318</v>
       </c>
       <c r="AC3">
-        <v>0.14436178255389</v>
+        <v>0.1962655739187665</v>
       </c>
       <c r="AD3">
-        <v>332.3</v>
+        <v>403.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>332.3</v>
+        <v>403.8</v>
       </c>
       <c r="AG3">
-        <v>113.4</v>
+        <v>-5.899999999999977</v>
       </c>
       <c r="AH3">
-        <v>0.03294763873603221</v>
+        <v>0.04185236624448084</v>
       </c>
       <c r="AI3">
-        <v>0.1261435675511521</v>
+        <v>0.1564267451770357</v>
       </c>
       <c r="AJ3">
-        <v>0.01149308793124417</v>
+        <v>-0.0006386318125236756</v>
       </c>
       <c r="AK3">
-        <v>0.04694874554939141</v>
+        <v>-0.002716765667449453</v>
       </c>
       <c r="AL3">
-        <v>30.2</v>
+        <v>35.5</v>
       </c>
       <c r="AM3">
-        <v>30.2</v>
+        <v>35.5</v>
       </c>
       <c r="AN3">
-        <v>0.4829941860465116</v>
+        <v>0.5876873817493815</v>
       </c>
       <c r="AO3">
-        <v>22.27814569536424</v>
+        <v>18.69014084507042</v>
       </c>
       <c r="AP3">
-        <v>0.1648255813953488</v>
+        <v>-0.008586814146412425</v>
       </c>
       <c r="AQ3">
-        <v>22.27814569536424</v>
+        <v>18.69014084507042</v>
       </c>
     </row>
     <row r="4">
@@ -862,46 +862,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.112</v>
+        <v>0.272</v>
       </c>
       <c r="E4">
-        <v>0.0268</v>
+        <v>0.454</v>
       </c>
       <c r="G4">
-        <v>0.318752451941938</v>
+        <v>0.1372446988422011</v>
       </c>
       <c r="H4">
-        <v>0.318752451941938</v>
+        <v>0.1372446988422011</v>
       </c>
       <c r="I4">
-        <v>0.1080816006276971</v>
+        <v>0.136334070508651</v>
       </c>
       <c r="J4">
-        <v>0.0878775990584543</v>
+        <v>0.1146171389232021</v>
       </c>
       <c r="K4">
-        <v>43.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L4">
-        <v>0.08473911337779522</v>
+        <v>0.1110966566931183</v>
       </c>
       <c r="M4">
-        <v>99.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="N4">
-        <v>0.09497100484836961</v>
+        <v>0.05285470085470086</v>
       </c>
       <c r="O4">
-        <v>2.3125</v>
+        <v>0.9051522248243559</v>
       </c>
       <c r="P4">
-        <v>99.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="Q4">
-        <v>0.09497100484836961</v>
+        <v>0.05285470085470086</v>
       </c>
       <c r="R4">
-        <v>2.3125</v>
+        <v>0.9051522248243559</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -910,67 +910,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9.550000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="V4">
-        <v>0.009078809772792091</v>
+        <v>0.007111111111111111</v>
       </c>
       <c r="W4">
-        <v>0.1087065928535481</v>
+        <v>0.3273284783441932</v>
       </c>
       <c r="X4">
-        <v>0.07806953922920157</v>
+        <v>0.06921598935675119</v>
       </c>
       <c r="Y4">
-        <v>0.0306370536243465</v>
+        <v>0.258112488987442</v>
       </c>
       <c r="Z4">
-        <v>0.9647993943981833</v>
+        <v>2.100560185817735</v>
       </c>
       <c r="AA4">
-        <v>0.08478425435276307</v>
+        <v>0.2407601986344186</v>
       </c>
       <c r="AB4">
-        <v>0.07402434694830444</v>
+        <v>0.06669735850572987</v>
       </c>
       <c r="AC4">
-        <v>0.01075990740445863</v>
+        <v>0.1740628401286887</v>
       </c>
       <c r="AD4">
-        <v>114.6</v>
+        <v>116.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>114.6</v>
+        <v>116.7</v>
       </c>
       <c r="AG4">
-        <v>105.05</v>
+        <v>106.3</v>
       </c>
       <c r="AH4">
-        <v>0.09824260608658379</v>
+        <v>0.07389817629179331</v>
       </c>
       <c r="AI4">
-        <v>0.3051930758988016</v>
+        <v>0.2455808080808081</v>
       </c>
       <c r="AJ4">
-        <v>0.09079908379791693</v>
+        <v>0.06775879653238144</v>
       </c>
       <c r="AK4">
-        <v>0.2870610739172018</v>
+        <v>0.2287005163511187</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AN4">
-        <v>2.024734982332155</v>
+        <v>1.088619402985075</v>
+      </c>
+      <c r="AO4">
+        <v>34.36065573770492</v>
       </c>
       <c r="AP4">
-        <v>1.856007067137809</v>
+        <v>0.9916044776119403</v>
+      </c>
+      <c r="AQ4">
+        <v>34.36065573770492</v>
       </c>
     </row>
   </sheetData>
